--- a/public/proforma-template.xlsx
+++ b/public/proforma-template.xlsx
@@ -3042,15 +3042,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>513000</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>42840</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1669720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>488620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3163,15 +3163,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>581760</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1669720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>488620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3676,7 +3676,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="19" x14ac:dyDescent="0.2">

--- a/public/proforma-template.xlsx
+++ b/public/proforma-template.xlsx
@@ -3042,15 +3042,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1669720</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>488620</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>513000</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>42840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3114,15 +3114,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>50800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1618920</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>18720</xdr:rowOff>
+      <xdr:colOff>1669720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>488620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3141,8 +3141,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="1618920" cy="447480"/>
+          <a:off x="50800" y="50800"/>
+          <a:ext cx="1618920" cy="437820"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3163,15 +3163,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1669720</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>488620</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>581760</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>21960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/public/proforma-template.xlsx
+++ b/public/proforma-template.xlsx
@@ -3993,22 +3993,22 @@
         <v>35</v>
       </c>
       <c r="B18" s="16">
-        <v>46876</v>
+        <f>Events!$O$31*0.5</f>
       </c>
       <c r="C18" s="16">
-        <v>93752</v>
+        <f>Events!$O$31*1</f>
       </c>
       <c r="D18" s="16">
-        <v>103127</v>
+        <f>Events!$O$31*1.1</f>
       </c>
       <c r="E18" s="16">
-        <v>113440</v>
+        <f>Events!$O$31*1.21</f>
       </c>
       <c r="F18" s="16">
-        <v>124784</v>
+        <f>Events!$O$31*1.331</f>
       </c>
       <c r="G18" s="16">
-        <v>137262</v>
+        <f>Events!$O$31*1.4641</f>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -4039,22 +4039,22 @@
         <v>37</v>
       </c>
       <c r="B20" s="16">
-        <v>2325</v>
+        <f>'Orgs &amp; Boards'!$D$17</f>
       </c>
       <c r="C20" s="16">
-        <v>2325</v>
+        <f>'Orgs &amp; Boards'!$D$17</f>
       </c>
       <c r="D20" s="16">
-        <v>2325</v>
+        <f>'Orgs &amp; Boards'!$D$17</f>
       </c>
       <c r="E20" s="16">
-        <v>2325</v>
+        <f>'Orgs &amp; Boards'!$D$17</f>
       </c>
       <c r="F20" s="16">
-        <v>2325</v>
+        <f>'Orgs &amp; Boards'!$D$17</f>
       </c>
       <c r="G20" s="16">
-        <v>2325</v>
+        <f>'Orgs &amp; Boards'!$D$17</f>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -4062,7 +4062,7 @@
         <v>38</v>
       </c>
       <c r="B21" s="16">
-        <v>120000</v>
+        <f>Events!$C$39</f>
       </c>
       <c r="C21" s="16">
         <v>0</v>
@@ -12262,6 +12262,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:B30 B35:B38">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -12687,6 +12692,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B16">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>

--- a/public/proforma-template.xlsx
+++ b/public/proforma-template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB5E789-DD48-814D-91D8-1A467B37A0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38020" yWindow="-7160" windowWidth="27900" windowHeight="19000" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38020" yWindow="-7160" windowWidth="27900" windowHeight="19000" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proforma" sheetId="1" r:id="rId1"/>

--- a/public/proforma-template.xlsx
+++ b/public/proforma-template.xlsx
@@ -4010,6 +4010,14 @@
       <c r="G18" s="16">
         <f>Events!$O$31*1.4641</f>
       </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Capital raised (investment)</t>
+        </is>
+      </c>
+      <c r="J18" s="15">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
@@ -5489,6 +5497,31 @@
       <c r="G84" s="19">
         <f>F84+G82</f>
         <v>53963014.625</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>Cash on hand (incl. investment)</t>
+        </is>
+      </c>
+      <c r="B85" s="19">
+        <f>$J$18+B84</f>
+      </c>
+      <c r="C85" s="19">
+        <f>$J$18+C84</f>
+      </c>
+      <c r="D85" s="19">
+        <f>$J$18+D84</f>
+      </c>
+      <c r="E85" s="19">
+        <f>$J$18+E84</f>
+      </c>
+      <c r="F85" s="19">
+        <f>$J$18+F84</f>
+      </c>
+      <c r="G85" s="19">
+        <f>$J$18+G84</f>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
@@ -11015,6 +11048,229 @@
       <c r="BU25" s="19">
         <f t="shared" si="11"/>
         <v>53963014.625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:73" x14ac:dyDescent="0.2">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>CASH ON HAND (incl. investment)</t>
+        </is>
+      </c>
+      <c r="B26" s="19">
+        <f>Proforma!$J$18+B25</f>
+      </c>
+      <c r="C26" s="19">
+        <f>Proforma!$J$18+C25</f>
+      </c>
+      <c r="D26" s="19">
+        <f>Proforma!$J$18+D25</f>
+      </c>
+      <c r="E26" s="19">
+        <f>Proforma!$J$18+E25</f>
+      </c>
+      <c r="F26" s="19">
+        <f>Proforma!$J$18+F25</f>
+      </c>
+      <c r="G26" s="19">
+        <f>Proforma!$J$18+G25</f>
+      </c>
+      <c r="H26" s="19">
+        <f>Proforma!$J$18+H25</f>
+      </c>
+      <c r="I26" s="19">
+        <f>Proforma!$J$18+I25</f>
+      </c>
+      <c r="J26" s="19">
+        <f>Proforma!$J$18+J25</f>
+      </c>
+      <c r="K26" s="19">
+        <f>Proforma!$J$18+K25</f>
+      </c>
+      <c r="L26" s="19">
+        <f>Proforma!$J$18+L25</f>
+      </c>
+      <c r="M26" s="19">
+        <f>Proforma!$J$18+M25</f>
+      </c>
+      <c r="N26" s="19">
+        <f>Proforma!$J$18+N25</f>
+      </c>
+      <c r="O26" s="19">
+        <f>Proforma!$J$18+O25</f>
+      </c>
+      <c r="P26" s="19">
+        <f>Proforma!$J$18+P25</f>
+      </c>
+      <c r="Q26" s="19">
+        <f>Proforma!$J$18+Q25</f>
+      </c>
+      <c r="R26" s="19">
+        <f>Proforma!$J$18+R25</f>
+      </c>
+      <c r="S26" s="19">
+        <f>Proforma!$J$18+S25</f>
+      </c>
+      <c r="T26" s="19">
+        <f>Proforma!$J$18+T25</f>
+      </c>
+      <c r="U26" s="19">
+        <f>Proforma!$J$18+U25</f>
+      </c>
+      <c r="V26" s="19">
+        <f>Proforma!$J$18+V25</f>
+      </c>
+      <c r="W26" s="19">
+        <f>Proforma!$J$18+W25</f>
+      </c>
+      <c r="X26" s="19">
+        <f>Proforma!$J$18+X25</f>
+      </c>
+      <c r="Y26" s="19">
+        <f>Proforma!$J$18+Y25</f>
+      </c>
+      <c r="Z26" s="19">
+        <f>Proforma!$J$18+Z25</f>
+      </c>
+      <c r="AA26" s="19">
+        <f>Proforma!$J$18+AA25</f>
+      </c>
+      <c r="AB26" s="19">
+        <f>Proforma!$J$18+AB25</f>
+      </c>
+      <c r="AC26" s="19">
+        <f>Proforma!$J$18+AC25</f>
+      </c>
+      <c r="AD26" s="19">
+        <f>Proforma!$J$18+AD25</f>
+      </c>
+      <c r="AE26" s="19">
+        <f>Proforma!$J$18+AE25</f>
+      </c>
+      <c r="AF26" s="19">
+        <f>Proforma!$J$18+AF25</f>
+      </c>
+      <c r="AG26" s="19">
+        <f>Proforma!$J$18+AG25</f>
+      </c>
+      <c r="AH26" s="19">
+        <f>Proforma!$J$18+AH25</f>
+      </c>
+      <c r="AI26" s="19">
+        <f>Proforma!$J$18+AI25</f>
+      </c>
+      <c r="AJ26" s="19">
+        <f>Proforma!$J$18+AJ25</f>
+      </c>
+      <c r="AK26" s="19">
+        <f>Proforma!$J$18+AK25</f>
+      </c>
+      <c r="AL26" s="19">
+        <f>Proforma!$J$18+AL25</f>
+      </c>
+      <c r="AM26" s="19">
+        <f>Proforma!$J$18+AM25</f>
+      </c>
+      <c r="AN26" s="19">
+        <f>Proforma!$J$18+AN25</f>
+      </c>
+      <c r="AO26" s="19">
+        <f>Proforma!$J$18+AO25</f>
+      </c>
+      <c r="AP26" s="19">
+        <f>Proforma!$J$18+AP25</f>
+      </c>
+      <c r="AQ26" s="19">
+        <f>Proforma!$J$18+AQ25</f>
+      </c>
+      <c r="AR26" s="19">
+        <f>Proforma!$J$18+AR25</f>
+      </c>
+      <c r="AS26" s="19">
+        <f>Proforma!$J$18+AS25</f>
+      </c>
+      <c r="AT26" s="19">
+        <f>Proforma!$J$18+AT25</f>
+      </c>
+      <c r="AU26" s="19">
+        <f>Proforma!$J$18+AU25</f>
+      </c>
+      <c r="AV26" s="19">
+        <f>Proforma!$J$18+AV25</f>
+      </c>
+      <c r="AW26" s="19">
+        <f>Proforma!$J$18+AW25</f>
+      </c>
+      <c r="AX26" s="19">
+        <f>Proforma!$J$18+AX25</f>
+      </c>
+      <c r="AY26" s="19">
+        <f>Proforma!$J$18+AY25</f>
+      </c>
+      <c r="AZ26" s="19">
+        <f>Proforma!$J$18+AZ25</f>
+      </c>
+      <c r="BA26" s="19">
+        <f>Proforma!$J$18+BA25</f>
+      </c>
+      <c r="BB26" s="19">
+        <f>Proforma!$J$18+BB25</f>
+      </c>
+      <c r="BC26" s="19">
+        <f>Proforma!$J$18+BC25</f>
+      </c>
+      <c r="BD26" s="19">
+        <f>Proforma!$J$18+BD25</f>
+      </c>
+      <c r="BE26" s="19">
+        <f>Proforma!$J$18+BE25</f>
+      </c>
+      <c r="BF26" s="19">
+        <f>Proforma!$J$18+BF25</f>
+      </c>
+      <c r="BG26" s="19">
+        <f>Proforma!$J$18+BG25</f>
+      </c>
+      <c r="BH26" s="19">
+        <f>Proforma!$J$18+BH25</f>
+      </c>
+      <c r="BI26" s="19">
+        <f>Proforma!$J$18+BI25</f>
+      </c>
+      <c r="BJ26" s="19">
+        <f>Proforma!$J$18+BJ25</f>
+      </c>
+      <c r="BK26" s="19">
+        <f>Proforma!$J$18+BK25</f>
+      </c>
+      <c r="BL26" s="19">
+        <f>Proforma!$J$18+BL25</f>
+      </c>
+      <c r="BM26" s="19">
+        <f>Proforma!$J$18+BM25</f>
+      </c>
+      <c r="BN26" s="19">
+        <f>Proforma!$J$18+BN25</f>
+      </c>
+      <c r="BO26" s="19">
+        <f>Proforma!$J$18+BO25</f>
+      </c>
+      <c r="BP26" s="19">
+        <f>Proforma!$J$18+BP25</f>
+      </c>
+      <c r="BQ26" s="19">
+        <f>Proforma!$J$18+BQ25</f>
+      </c>
+      <c r="BR26" s="19">
+        <f>Proforma!$J$18+BR25</f>
+      </c>
+      <c r="BS26" s="19">
+        <f>Proforma!$J$18+BS25</f>
+      </c>
+      <c r="BT26" s="19">
+        <f>Proforma!$J$18+BT25</f>
+      </c>
+      <c r="BU26" s="19">
+        <f>Proforma!$J$18+BU25</f>
       </c>
     </row>
     <row r="27" spans="1:73" x14ac:dyDescent="0.2">
